--- a/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/validation/D3_operational_envelope_diagnostics.xlsx
+++ b/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/validation/D3_operational_envelope_diagnostics.xlsx
@@ -888,19 +888,19 @@
         <v>0.004231770833333333</v>
       </c>
       <c r="D2">
-        <v>0.02766927083333333</v>
+        <v>0.01432291666666667</v>
       </c>
       <c r="E2">
         <v>9.156512909776618E-05</v>
       </c>
       <c r="F2">
-        <v>0.008297976501305484</v>
+        <v>0.003815818102697998</v>
       </c>
       <c r="G2">
         <v>0.02</v>
       </c>
       <c r="H2">
-        <v>7.927034085789853</v>
+        <v>7.353848386063327</v>
       </c>
       <c r="I2">
         <v>0.004231770833333333</v>
@@ -950,19 +950,19 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0.06673177083333333</v>
+        <v>0.01985677083333333</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.01285628807658834</v>
+        <v>0.004422323759791123</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>7.291502311270616</v>
+        <v>6.763859768196781</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1012,19 +1012,19 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>0.0029296875</v>
+        <v>0.0003255208333333333</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.0007968885987815492</v>
+        <v>1.087902523933855E-05</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>4.197219083227807</v>
+        <v>2.70841903412697</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1136,19 +1136,19 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0.05110677083333334</v>
+        <v>0.02604166666666667</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.02062729465154208</v>
+        <v>0.0107327297759835</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.692245192185338</v>
+        <v>7.057515687978221</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1198,19 +1198,19 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0.03841145833333334</v>
+        <v>0.01822916666666667</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0.01709993070335184</v>
+        <v>0.00991682573812815</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>2.886189252768078</v>
+        <v>2.258255229898325</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1260,19 +1260,19 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0.4508463541666667</v>
+        <v>0.0068359375</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0.05474846459088568</v>
+        <v>0.0009437554395126197</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>5.534821397557533</v>
+        <v>3.886398657108568</v>
       </c>
       <c r="I8">
         <v>0</v>
